--- a/output/summary_tables/Corrective Action Module Summary Tables.xlsx
+++ b/output/summary_tables/Corrective Action Module Summary Tables.xlsx
@@ -8,6 +8,7 @@
   <sheets>
     <sheet name="Categorical" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Quantitative" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dummy" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -38,7 +39,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -58,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA6C9EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -87,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyBorder="1" applyFont="1" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
@@ -126,6 +132,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="1" numFmtId="167" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyBorder="1" applyFill="1" applyFont="1" borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -453,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
@@ -467,7 +477,7 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Corrective Action - investigation and cleanup events at facilities required to remediate hazardous-waste releases.</t>
+          <t>Corrective Action - investigation and cleanup events at facilities required to remediate hazardous-waste releases. Summarized from the CA_MASTER master file.</t>
         </is>
       </c>
       <c r="B1" s="7"/>
@@ -479,7 +489,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Identifier: HANDLER_ID, one row per corrective-action event.</t>
+          <t>Identifier: HANDLER_ID, one row per corrective-action event x area x process unit x authority x citation combination.</t>
         </is>
       </c>
       <c r="B2" s="7"/>
@@ -495,7 +505,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <v>193200</v>
+        <v>309872</v>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
@@ -532,7 +542,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>6 other columns not summarized (identifiers, names, and descriptions / free-text fields).</t>
+          <t>9 other columns are not summarized because they hold record identifiers, personal names and staff identifiers, correspondence addresses and contact details, free-text notes, or the description text paired with a code that is summarized here. They are named below the table.</t>
         </is>
       </c>
       <c r="C5" s="7"/>
@@ -581,7 +591,7 @@
               <color rgb="FF000000"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t xml:space="preserve">EVENT_AGENCY
+            <t xml:space="preserve">EVENT_ACTIVITY_LOCATION
 </t>
           </r>
           <r>
@@ -590,7 +600,7 @@
               <color rgb="FF666666"/>
               <rFont val="Calibri"/>
             </rPr>
-            <t>Agency responsible for the corrective-action event.</t>
+            <t>State or territory whose implementing agency is responsible for the event.</t>
           </r>
         </is>
       </c>
@@ -601,18 +611,18 @@
         </is>
       </c>
       <c r="C7" s="11">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>S - State</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E7" s="12">
-        <v>69</v>
+        <v>14.4</v>
       </c>
       <c r="F7" s="10">
-        <v>133305</v>
+        <v>44731</v>
       </c>
     </row>
     <row r="8">
@@ -621,14 +631,14 @@
       <c r="C8" s="11"/>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>E - EPA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E8" s="12">
-        <v>30.3</v>
+        <v>9.8</v>
       </c>
       <c r="F8" s="10">
-        <v>58622</v>
+        <v>30214</v>
       </c>
     </row>
     <row r="9">
@@ -637,14 +647,14 @@
       <c r="C9" s="11"/>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>J - Joint with State Lead</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E9" s="12">
-        <v>0.6</v>
+        <v>7.4</v>
       </c>
       <c r="F9" s="10">
-        <v>1165</v>
+        <v>23041</v>
       </c>
     </row>
     <row r="10">
@@ -653,57 +663,30 @@
       <c r="C10" s="11"/>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>P - Joint with EPA Lead</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="E10" s="12">
-        <v>0.1</v>
+        <v>7.1</v>
       </c>
       <c r="F10" s="10">
-        <v>108</v>
+        <v>21851</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF000000"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t xml:space="preserve">EVENT_ACTIVITY_LOCATION
-</t>
-          </r>
-          <r>
-            <rPr>
-              <sz val="12"/>
-              <color rgb="FF666666"/>
-              <rFont val="Calibri"/>
-            </rPr>
-            <t>State or territory whose implementing agency is responsible for the event.</t>
-          </r>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>0%
-(0)</t>
-        </is>
-      </c>
-      <c r="C11" s="11">
-        <v>59</v>
-      </c>
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="E11" s="12">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="F11" s="10">
-        <v>20253</v>
+        <v>21140</v>
       </c>
     </row>
     <row r="12">
@@ -712,30 +695,57 @@
       <c r="C12" s="11"/>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>All Other (54)</t>
         </is>
       </c>
       <c r="E12" s="12">
-        <v>9.5</v>
+        <v>54.5</v>
       </c>
       <c r="F12" s="10">
-        <v>18304</v>
+        <v>168895</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EVENT_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency responsible for the corrective-action event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>0%
+(0)</t>
+        </is>
+      </c>
+      <c r="C13" s="11">
+        <v>4</v>
+      </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>S - State</t>
         </is>
       </c>
       <c r="E13" s="12">
-        <v>6.3</v>
+        <v>77</v>
       </c>
       <c r="F13" s="10">
-        <v>12196</v>
+        <v>238451</v>
       </c>
     </row>
     <row r="14">
@@ -744,14 +754,14 @@
       <c r="C14" s="11"/>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>E - EPA</t>
         </is>
       </c>
       <c r="E14" s="12">
-        <v>6</v>
+        <v>22.2</v>
       </c>
       <c r="F14" s="10">
-        <v>11584</v>
+        <v>68698</v>
       </c>
     </row>
     <row r="15">
@@ -760,14 +770,14 @@
       <c r="C15" s="11"/>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>J - Joint with State Lead</t>
         </is>
       </c>
       <c r="E15" s="12">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="F15" s="10">
-        <v>11192</v>
+        <v>2579</v>
       </c>
     </row>
     <row r="16">
@@ -776,14 +786,14 @@
       <c r="C16" s="11"/>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>All Other (54)</t>
+          <t>P - Joint with EPA Lead</t>
         </is>
       </c>
       <c r="E16" s="12">
-        <v>61.9</v>
+        <v>0</v>
       </c>
       <c r="F16" s="10">
-        <v>119671</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -823,10 +833,10 @@
         </is>
       </c>
       <c r="E17" s="12">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="F17" s="10">
-        <v>134316</v>
+        <v>214722</v>
       </c>
     </row>
     <row r="18">
@@ -835,14 +845,14 @@
       <c r="C18" s="11"/>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E18" s="12">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="F18" s="10">
-        <v>10846</v>
+        <v>18981</v>
       </c>
     </row>
     <row r="19">
@@ -851,14 +861,14 @@
       <c r="C19" s="11"/>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E19" s="12">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="F19" s="10">
-        <v>7517</v>
+        <v>13672</v>
       </c>
     </row>
     <row r="20">
@@ -867,14 +877,14 @@
       <c r="C20" s="11"/>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E20" s="12">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="F20" s="10">
-        <v>7350</v>
+        <v>13590</v>
       </c>
     </row>
     <row r="21">
@@ -887,10 +897,10 @@
         </is>
       </c>
       <c r="E21" s="12">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F21" s="10">
-        <v>5754</v>
+        <v>10128</v>
       </c>
     </row>
     <row r="22">
@@ -903,10 +913,10 @@
         </is>
       </c>
       <c r="E22" s="12">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="F22" s="10">
-        <v>27417</v>
+        <v>38779</v>
       </c>
     </row>
     <row r="23">
@@ -942,14 +952,14 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>CA110 - Investigation Workplan Received</t>
+          <t>CA150 - Investigation Workplan Approved</t>
         </is>
       </c>
       <c r="E23" s="12">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="F23" s="10">
-        <v>7074</v>
+        <v>11697</v>
       </c>
     </row>
     <row r="24">
@@ -958,14 +968,14 @@
       <c r="C24" s="11"/>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>CA400 - Remedy Decision</t>
+          <t>CA110 - Investigation Workplan Received</t>
         </is>
       </c>
       <c r="E24" s="12">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F24" s="10">
-        <v>6641</v>
+        <v>11689</v>
       </c>
     </row>
     <row r="25">
@@ -974,14 +984,14 @@
       <c r="C25" s="11"/>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>CA150 - Investigation Workplan Approved</t>
+          <t>CA400 - Remedy Decision</t>
         </is>
       </c>
       <c r="E25" s="12">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="F25" s="10">
-        <v>6417</v>
+        <v>11540</v>
       </c>
     </row>
     <row r="26">
@@ -994,10 +1004,10 @@
         </is>
       </c>
       <c r="E26" s="12">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="F26" s="10">
-        <v>6226</v>
+        <v>11101</v>
       </c>
     </row>
     <row r="27">
@@ -1006,14 +1016,14 @@
       <c r="C27" s="11"/>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>CA725YE - Current Human Exposures Under Control Determination - Under Control</t>
+          <t>CA100 - Investigation Imposition</t>
         </is>
       </c>
       <c r="E27" s="12">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="F27" s="10">
-        <v>5137</v>
+        <v>10753</v>
       </c>
     </row>
     <row r="28">
@@ -1026,62 +1036,1789 @@
         </is>
       </c>
       <c r="E28" s="12">
-        <v>83.7</v>
+        <v>81.7</v>
       </c>
       <c r="F28" s="10">
-        <v>161705</v>
+        <v>253092</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">RESPONSIBLE_PERSON_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that owns the record of the person responsible for the event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>21.7%
+(67302)</t>
+        </is>
+      </c>
+      <c r="C29" s="11">
+        <v>56</v>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E29" s="12">
+        <v>14.1</v>
+      </c>
+      <c r="F29" s="10">
+        <v>43751</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E30" s="12">
+        <v>8.9</v>
+      </c>
+      <c r="F30" s="10">
+        <v>27682</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="E31" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="F31" s="10">
+        <v>20631</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E32" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="F32" s="10">
+        <v>20031</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>05 - EPA Region 5</t>
+        </is>
+      </c>
+      <c r="E33" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="F33" s="10">
+        <v>11540</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>All Other (51)</t>
+        </is>
+      </c>
+      <c r="E34" s="12">
+        <v>38.4</v>
+      </c>
+      <c r="F34" s="10">
+        <v>118935</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SUBORGANIZATION_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that owns the suborganization record on the event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>32.9%
+(102013)</t>
+        </is>
+      </c>
+      <c r="C35" s="11">
+        <v>42</v>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E35" s="12">
+        <v>14</v>
+      </c>
+      <c r="F35" s="10">
+        <v>43459</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E36" s="12">
+        <v>9</v>
+      </c>
+      <c r="F36" s="10">
+        <v>27815</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="E37" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="F37" s="10">
+        <v>19796</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E38" s="12">
+        <v>6</v>
+      </c>
+      <c r="F38" s="10">
+        <v>18724</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>04 - EPA Region 4</t>
+        </is>
+      </c>
+      <c r="E39" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="F39" s="10">
+        <v>9996</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>All Other (37)</t>
+        </is>
+      </c>
+      <c r="E40" s="12">
+        <v>28.4</v>
+      </c>
+      <c r="F40" s="10">
+        <v>88069</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">SUBORGANIZATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Suborganization within the implementing agency that handles the event (codes are agency-specific).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>32.9%
+(102013)</t>
+        </is>
+      </c>
+      <c r="C41" s="11">
+        <v>343</v>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="E41" s="12">
+        <v>9.6</v>
+      </c>
+      <c r="F41" s="10">
+        <v>29659</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="E42" s="12">
+        <v>5.7</v>
+      </c>
+      <c r="F42" s="10">
+        <v>17733</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>HW</t>
+        </is>
+      </c>
+      <c r="E43" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="F43" s="10">
+        <v>17407</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="E44" s="12">
+        <v>5</v>
+      </c>
+      <c r="F44" s="10">
+        <v>15626</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>RPB</t>
+        </is>
+      </c>
+      <c r="E45" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="F45" s="10">
+        <v>8825</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>All Other (338)</t>
+        </is>
+      </c>
+      <c r="E46" s="12">
+        <v>38.3</v>
+      </c>
+      <c r="F46" s="10">
+        <v>118609</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">EPA_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>EPA region that owns the record of the EPA contact for the area.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>95.3%
+(295458)</t>
+        </is>
+      </c>
+      <c r="C47" s="11">
+        <v>10</v>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>07 - EPA Region 7</t>
+        </is>
+      </c>
+      <c r="E47" s="12">
+        <v>2.3</v>
+      </c>
+      <c r="F47" s="10">
+        <v>7099</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>03 - EPA Region 3</t>
+        </is>
+      </c>
+      <c r="E48" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="F48" s="10">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>04 - EPA Region 4</t>
+        </is>
+      </c>
+      <c r="E49" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="F49" s="10">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>02 - EPA Region 2</t>
+        </is>
+      </c>
+      <c r="E50" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F50" s="10">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>08 - EPA Region 8</t>
+        </is>
+      </c>
+      <c r="E51" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F51" s="10">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>All Other (5)</t>
+        </is>
+      </c>
+      <c r="E52" s="12">
+        <v>0.4</v>
+      </c>
+      <c r="F52" s="10">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">STATE_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State that owns the record of the state contact for the area.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>77.7%
+(240823)</t>
+        </is>
+      </c>
+      <c r="C53" s="11">
+        <v>39</v>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E53" s="12">
+        <v>5.1</v>
+      </c>
+      <c r="F53" s="10">
+        <v>15951</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E54" s="12">
+        <v>5</v>
+      </c>
+      <c r="F54" s="10">
+        <v>15515</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="E55" s="12">
+        <v>2.6</v>
+      </c>
+      <c r="F55" s="10">
+        <v>7961</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="E56" s="12">
+        <v>2.3</v>
+      </c>
+      <c r="F56" s="10">
+        <v>7078</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E57" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="F57" s="10">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>All Other (34)</t>
+        </is>
+      </c>
+      <c r="E58" s="12">
+        <v>5.9</v>
+      </c>
+      <c r="F58" s="10">
+        <v>18426</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_ACTIVITY_LOCATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>State or territory whose implementing agency is responsible for the legal authority.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>6.4%
+(19728)</t>
+        </is>
+      </c>
+      <c r="C59" s="11">
+        <v>57</v>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E59" s="12">
+        <v>14.1</v>
+      </c>
+      <c r="F59" s="10">
+        <v>43783</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E60" s="12">
+        <v>9</v>
+      </c>
+      <c r="F60" s="10">
+        <v>28029</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E61" s="12">
+        <v>7.4</v>
+      </c>
+      <c r="F61" s="10">
+        <v>22840</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="E62" s="12">
+        <v>7</v>
+      </c>
+      <c r="F62" s="10">
+        <v>21786</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="E63" s="12">
+        <v>5.6</v>
+      </c>
+      <c r="F63" s="10">
+        <v>17412</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>All Other (52)</t>
+        </is>
+      </c>
+      <c r="E64" s="12">
+        <v>50.4</v>
+      </c>
+      <c r="F64" s="10">
+        <v>156294</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_AGENCY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Agency behind the legal authority that ordered the event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>6.4%
+(19728)</t>
+        </is>
+      </c>
+      <c r="C65" s="11">
+        <v>4</v>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>S - State</t>
+        </is>
+      </c>
+      <c r="E65" s="12">
+        <v>66.7</v>
+      </c>
+      <c r="F65" s="10">
+        <v>206636</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>E - EPA</t>
+        </is>
+      </c>
+      <c r="E66" s="12">
+        <v>24.2</v>
+      </c>
+      <c r="F66" s="10">
+        <v>74862</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>J - Joint with State Lead</t>
+        </is>
+      </c>
+      <c r="E67" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="F67" s="10">
+        <v>8314</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>P - Joint with EPA Lead</t>
+        </is>
+      </c>
+      <c r="E68" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="F68" s="10">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the authority code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>6.4%
+(19728)</t>
+        </is>
+      </c>
+      <c r="C69" s="11">
+        <v>1</v>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E69" s="12">
+        <v>93.6</v>
+      </c>
+      <c r="F69" s="10">
+        <v>290144</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_TYPE
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Type of legal authority (order, permit, statute) behind the event.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>6.4%
+(19728)</t>
+        </is>
+      </c>
+      <c r="C70" s="11">
+        <v>19</v>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>O - Operating Permit</t>
+        </is>
+      </c>
+      <c r="E70" s="12">
+        <v>31.7</v>
+      </c>
+      <c r="F70" s="10">
+        <v>98324</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>A - Consent Order</t>
+        </is>
+      </c>
+      <c r="E71" s="12">
+        <v>15.8</v>
+      </c>
+      <c r="F71" s="10">
+        <v>48888</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>P - Post-Closure Permit</t>
+        </is>
+      </c>
+      <c r="E72" s="12">
+        <v>13.7</v>
+      </c>
+      <c r="F72" s="10">
+        <v>42470</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>V - Voluntary CA</t>
+        </is>
+      </c>
+      <c r="E73" s="12">
+        <v>6.7</v>
+      </c>
+      <c r="F73" s="10">
+        <v>20719</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Z - Other</t>
+        </is>
+      </c>
+      <c r="E74" s="12">
+        <v>5.3</v>
+      </c>
+      <c r="F74" s="10">
+        <v>16466</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>All Other (14)</t>
+        </is>
+      </c>
+      <c r="E75" s="12">
+        <v>20.4</v>
+      </c>
+      <c r="F75" s="10">
+        <v>63277</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_REPOSITORY
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Repository code recording where the authority document is held.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>87.4%
+(270758)</t>
+        </is>
+      </c>
+      <c r="C76" s="11">
+        <v>4</v>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" s="12">
+        <v>9</v>
+      </c>
+      <c r="F76" s="10">
+        <v>27848</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E77" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="F77" s="10">
+        <v>9520</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E78" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F78" s="10">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E79" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="F79" s="10">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_RESPONSIBLE_PERSON_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that owns the record of the person responsible for the authority.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>25.4%
+(78843)</t>
+        </is>
+      </c>
+      <c r="C80" s="11">
+        <v>50</v>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E80" s="12">
+        <v>13.8</v>
+      </c>
+      <c r="F80" s="10">
+        <v>42703</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E81" s="12">
+        <v>6.5</v>
+      </c>
+      <c r="F81" s="10">
+        <v>20054</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="E82" s="12">
+        <v>6.2</v>
+      </c>
+      <c r="F82" s="10">
+        <v>19320</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>04 - EPA Region 4</t>
+        </is>
+      </c>
+      <c r="E83" s="12">
+        <v>6.1</v>
+      </c>
+      <c r="F83" s="10">
+        <v>18785</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E84" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="F84" s="10">
+        <v>17096</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>All Other (45)</t>
+        </is>
+      </c>
+      <c r="E85" s="12">
+        <v>36.5</v>
+      </c>
+      <c r="F85" s="10">
+        <v>113071</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_SUBORGANIZATION_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that owns the suborganization record on the authority.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>40.5%
+(125451)</t>
+        </is>
+      </c>
+      <c r="C86" s="11">
+        <v>38</v>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E86" s="12">
+        <v>13.6</v>
+      </c>
+      <c r="F86" s="10">
+        <v>42105</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E87" s="12">
+        <v>6.4</v>
+      </c>
+      <c r="F87" s="10">
+        <v>19772</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E88" s="12">
+        <v>6.2</v>
+      </c>
+      <c r="F88" s="10">
+        <v>19233</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="E89" s="12">
+        <v>6.1</v>
+      </c>
+      <c r="F89" s="10">
+        <v>18815</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>04 - EPA Region 4</t>
+        </is>
+      </c>
+      <c r="E90" s="12">
+        <v>3.8</v>
+      </c>
+      <c r="F90" s="10">
+        <v>11882</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>All Other (33)</t>
+        </is>
+      </c>
+      <c r="E91" s="12">
+        <v>23.4</v>
+      </c>
+      <c r="F91" s="10">
+        <v>72614</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">AUTHORITY_SUBORGANIZATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Suborganization within the agency that administers the authority (codes are agency-specific).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>40.5%
+(125451)</t>
+        </is>
+      </c>
+      <c r="C92" s="11">
+        <v>186</v>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="E92" s="12">
+        <v>6</v>
+      </c>
+      <c r="F92" s="10">
+        <v>18485</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>HW</t>
+        </is>
+      </c>
+      <c r="E93" s="12">
+        <v>5.8</v>
+      </c>
+      <c r="F93" s="10">
+        <v>17887</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>HWC</t>
+        </is>
+      </c>
+      <c r="E94" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="F94" s="10">
+        <v>16225</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="E95" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="F95" s="10">
+        <v>11012</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>C&amp;P</t>
+        </is>
+      </c>
+      <c r="E96" s="12">
+        <v>2.7</v>
+      </c>
+      <c r="F96" s="10">
+        <v>8397</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>All Other (181)</t>
+        </is>
+      </c>
+      <c r="E97" s="12">
+        <v>36.3</v>
+      </c>
+      <c r="F97" s="10">
+        <v>112415</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">STATUTORY_OWNER
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Organization that defines the statutory-citation code list.</t>
+          </r>
+        </is>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>6.7%
+(20626)</t>
+        </is>
+      </c>
+      <c r="C98" s="11">
+        <v>1</v>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>HQ - Nationally Defined Values</t>
+        </is>
+      </c>
+      <c r="E98" s="12">
+        <v>93.3</v>
+      </c>
+      <c r="F98" s="10">
+        <v>289246</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF000000"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t xml:space="preserve">STATUTORY_CITATION
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="12"/>
+              <color rgb="FF666666"/>
+              <rFont val="Calibri"/>
+            </rPr>
+            <t>Statutory citation the authority rests on (the module lookup ships these codes without descriptions).</t>
+          </r>
+        </is>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>6.7%
+(20626)</t>
+        </is>
+      </c>
+      <c r="C99" s="11">
+        <v>22</v>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E99" s="12">
+        <v>43.6</v>
+      </c>
+      <c r="F99" s="10">
+        <v>135013</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E100" s="12">
+        <v>19.9</v>
+      </c>
+      <c r="F100" s="10">
+        <v>61593</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E101" s="12">
+        <v>16.1</v>
+      </c>
+      <c r="F101" s="10">
+        <v>49989</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E102" s="12">
+        <v>2.9</v>
+      </c>
+      <c r="F102" s="10">
+        <v>8912</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E103" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="F103" s="10">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>All Other (17)</t>
+        </is>
+      </c>
+      <c r="E104" s="12">
+        <v>8.4</v>
+      </c>
+      <c r="F104" s="10">
+        <v>25949</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>Notes on missing values:
+SUBORGANIZATION_OWNER / SUBORGANIZATION: Missing. Only the agencies that record a handling suborganization fill these.
+EPA_OWNER / STATE_OWNER: Not applicable. Each area names at most one of the two contacts, so both columns are blank on most rows.
+AUTHORITY_AGENCY / AUTHORITY_TYPE / AUTHORITY_OWNER: Not applicable. Events with no linked authority keep those columns blank.
+AUTHORITY_REPOSITORY: Missing. Recorded only where the agency logged where the document is held.
+STATUTORY_OWNER / STATUTORY_CITATION: Not applicable. Blank when the event has no linked authority.</t>
+        </is>
+      </c>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
+      <c r="D106" s="14"/>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="14"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
+      <c r="D107" s="14"/>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="14"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="14"/>
+      <c r="D108" s="14"/>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="14"/>
+      <c r="D110" s="14"/>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="14"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="14" t="inlineStr">
         <is>
           <t>Variables dropped (present in the source file but not summarized):
-'EVENT_SEQ', 'RESPONSIBLE_PERSON_OWNER', 'RESPONSIBLE_PERSON',
-'SUBORGANIZATION_OWNER', 'SUBORGANIZATION', 'PUBLIC_NOTES'</t>
-        </is>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+'RESPONSIBLE_PERSON', 'PUBLIC_NOTES', 'AREA_HANDLER_ID', 'AREA_NAME',
+'EPA_PERSON_ID', 'STATE_PERSON_ID', 'UNIT_HANDLER_ID',
+'AUTHORITY_HANDLER_ID', 'AUTHORITY_RESPONSIBLE_PERSON'</t>
+        </is>
+      </c>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
+      <c r="D113" s="14"/>
+      <c r="E113" s="14"/>
+      <c r="F113" s="14"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
+      <c r="D114" s="14"/>
+      <c r="E114" s="14"/>
+      <c r="F114" s="14"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
+      <c r="D115" s="14"/>
+      <c r="E115" s="14"/>
+      <c r="F115" s="14"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="58">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:F4"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="A7:A12"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C7:C12"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="C17:C22"/>
     <mergeCell ref="A23:A28"/>
     <mergeCell ref="B23:B28"/>
     <mergeCell ref="C23:C28"/>
-    <mergeCell ref="A30:F32"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="C29:C34"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="C35:C40"/>
+    <mergeCell ref="A41:A46"/>
+    <mergeCell ref="B41:B46"/>
+    <mergeCell ref="C41:C46"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="B47:B52"/>
+    <mergeCell ref="C47:C52"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="B53:B58"/>
+    <mergeCell ref="C53:C58"/>
+    <mergeCell ref="A59:A64"/>
+    <mergeCell ref="B59:B64"/>
+    <mergeCell ref="C59:C64"/>
+    <mergeCell ref="A65:A68"/>
+    <mergeCell ref="B65:B68"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="A76:A79"/>
+    <mergeCell ref="B76:B79"/>
+    <mergeCell ref="C76:C79"/>
+    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="B80:B85"/>
+    <mergeCell ref="C80:C85"/>
+    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="B86:B91"/>
+    <mergeCell ref="C86:C91"/>
+    <mergeCell ref="A92:A97"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="C92:C97"/>
+    <mergeCell ref="A99:A104"/>
+    <mergeCell ref="B99:B104"/>
+    <mergeCell ref="C99:C104"/>
+    <mergeCell ref="A106:F111"/>
+    <mergeCell ref="A113:F116"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1091,7 +2828,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="23"/>
@@ -1142,19 +2879,19 @@
         </is>
       </c>
       <c r="B2" s="10">
-        <v>19760</v>
+        <v>35488</v>
       </c>
       <c r="C2" s="10">
-        <v>89.8</v>
+        <v>88.5</v>
       </c>
       <c r="D2" s="21">
         <v>18505</v>
       </c>
       <c r="E2" s="21">
-        <v>32671</v>
+        <v>32843</v>
       </c>
       <c r="F2" s="21">
-        <v>45064</v>
+        <v>44862</v>
       </c>
       <c r="G2" s="21">
         <v>414520</v>
@@ -1167,19 +2904,19 @@
         </is>
       </c>
       <c r="B3" s="10">
-        <v>1177</v>
+        <v>2150</v>
       </c>
       <c r="C3" s="10">
-        <v>99.4</v>
+        <v>99.3</v>
       </c>
       <c r="D3" s="21">
         <v>32354</v>
       </c>
       <c r="E3" s="21">
-        <v>36799</v>
+        <v>37041</v>
       </c>
       <c r="F3" s="21">
-        <v>46152</v>
+        <v>46112</v>
       </c>
       <c r="G3" s="21">
         <v>55792</v>
@@ -1192,19 +2929,19 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <v>189551</v>
+        <v>304950</v>
       </c>
       <c r="C4" s="10">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="D4" s="21">
         <v>367</v>
       </c>
       <c r="E4" s="21">
-        <v>32874</v>
+        <v>33045</v>
       </c>
       <c r="F4" s="21">
-        <v>44396</v>
+        <v>44370</v>
       </c>
       <c r="G4" s="21">
         <v>46204</v>
@@ -1217,7 +2954,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <v>193155</v>
+        <v>309821</v>
       </c>
       <c r="C5" s="10">
         <v>0</v>
@@ -1226,51 +2963,525 @@
         <v>367</v>
       </c>
       <c r="E5" s="21">
-        <v>32874</v>
+        <v>33053</v>
       </c>
       <c r="F5" s="21">
-        <v>44428</v>
+        <v>44375</v>
       </c>
       <c r="G5" s="21">
         <v>414520</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>AUTHORITY_EFFECTIVE_DATE</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <v>290144</v>
+      </c>
+      <c r="C6" s="10">
+        <v>6.4</v>
+      </c>
+      <c r="D6" s="21">
+        <v>25569</v>
+      </c>
+      <c r="E6" s="21">
+        <v>31929</v>
+      </c>
+      <c r="F6" s="21">
+        <v>41961</v>
+      </c>
+      <c r="G6" s="21">
+        <v>46169</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>AUTHORITY_ISSUE_DATE</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <v>240611</v>
+      </c>
+      <c r="C7" s="10">
+        <v>22.4</v>
+      </c>
+      <c r="D7" s="21">
+        <v>25569</v>
+      </c>
+      <c r="E7" s="21">
+        <v>32084</v>
+      </c>
+      <c r="F7" s="21">
+        <v>41766</v>
+      </c>
+      <c r="G7" s="21">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>AUTHORITY_END_DATE</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <v>15777</v>
+      </c>
+      <c r="C8" s="10">
+        <v>94.9</v>
+      </c>
+      <c r="D8" s="21">
+        <v>652</v>
+      </c>
+      <c r="E8" s="21">
+        <v>1034</v>
+      </c>
+      <c r="F8" s="21">
+        <v>46658</v>
+      </c>
+      <c r="G8" s="21">
+        <v>49703</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>EVENT_SEQ</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <v>309872</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10">
+        <v>1</v>
+      </c>
+      <c r="E9" s="10">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <v>148</v>
+      </c>
+      <c r="G9" s="10">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>AREA_SEQ</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <v>299678</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3.3</v>
+      </c>
+      <c r="D10" s="10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10">
+        <v>141</v>
+      </c>
+      <c r="G10" s="10">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>UNIT_SEQ</t>
+        </is>
+      </c>
+      <c r="B11" s="10">
+        <v>854</v>
+      </c>
+      <c r="C11" s="10">
+        <v>99.7</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="10">
+        <v>1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>12</v>
+      </c>
+      <c r="G11" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AREA_ACREAGE</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <v>89620</v>
+      </c>
+      <c r="C12" s="10">
+        <v>71.1</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="F12" s="10">
+        <v>3708</v>
+      </c>
+      <c r="G12" s="10">
+        <v>2669225</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Notes on missing values:
 SCHEDULE_DATE_ORIG: Not applicable. Most events are recorded as completed actuals. Only scheduled events have a scheduled date.
-SCHEDULE_DATE_NEW: Not applicable. Only rescheduled events have a revised date.</t>
-        </is>
-      </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+SCHEDULE_DATE_NEW: Not applicable. Only rescheduled events have a revised date.
+UNIT_SEQ: Not applicable. Very few events link to a specific process unit.
+AUTHORITY_* dates / AREA_ACREAGE: Not applicable. Blank when the event has no linked authority or area.</t>
+        </is>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A14:G18"/>
+  </mergeCells>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="28.5"/>
+    <col min="2" max="9" bestFit="1" customWidth="1" hidden="false" width="12.664"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Variables</t>
+        </is>
+      </c>
+      <c r="B1" s="23" t="inlineStr">
+        <is>
+          <t>N Missing</t>
+        </is>
+      </c>
+      <c r="C1" s="23" t="inlineStr">
+        <is>
+          <t>% Missing</t>
+        </is>
+      </c>
+      <c r="D1" s="23" t="inlineStr">
+        <is>
+          <t>Yes N</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>Yes %</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>No N</t>
+        </is>
+      </c>
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>No %</t>
+        </is>
+      </c>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>Unknown N</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>Unknown %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>ENTIRE_FACILITY_IND</t>
+        </is>
+      </c>
+      <c r="B2" s="10">
+        <v>10194</v>
+      </c>
+      <c r="C2" s="10">
+        <v>3.29</v>
+      </c>
+      <c r="D2" s="10">
+        <v>121970</v>
+      </c>
+      <c r="E2" s="10">
+        <v>39.36</v>
+      </c>
+      <c r="F2" s="10">
+        <v>177708</v>
+      </c>
+      <c r="G2" s="10">
+        <v>57.35</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>REGULATED_UNIT_IND</t>
+        </is>
+      </c>
+      <c r="B3" s="10">
+        <v>270044</v>
+      </c>
+      <c r="C3" s="10">
+        <v>87.15</v>
+      </c>
+      <c r="D3" s="10">
+        <v>7078</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2.28</v>
+      </c>
+      <c r="F3" s="10">
+        <v>32750</v>
+      </c>
+      <c r="G3" s="10">
+        <v>10.57</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>AIR_RELEASE_IND</t>
+        </is>
+      </c>
+      <c r="B4" s="10">
+        <v>273197</v>
+      </c>
+      <c r="C4" s="10">
+        <v>88.16</v>
+      </c>
+      <c r="D4" s="10">
+        <v>14902</v>
+      </c>
+      <c r="E4" s="10">
+        <v>4.81</v>
+      </c>
+      <c r="F4" s="10">
+        <v>21773</v>
+      </c>
+      <c r="G4" s="10">
+        <v>7.03</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>GROUNDWATER_RELEASE_IND</t>
+        </is>
+      </c>
+      <c r="B5" s="10">
+        <v>188000</v>
+      </c>
+      <c r="C5" s="10">
+        <v>60.67</v>
+      </c>
+      <c r="D5" s="10">
+        <v>117577</v>
+      </c>
+      <c r="E5" s="10">
+        <v>37.94</v>
+      </c>
+      <c r="F5" s="10">
+        <v>4295</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1.39</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>SOIL_RELEASE_IND</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <v>165952</v>
+      </c>
+      <c r="C6" s="10">
+        <v>53.56</v>
+      </c>
+      <c r="D6" s="10">
+        <v>136006</v>
+      </c>
+      <c r="E6" s="10">
+        <v>43.89</v>
+      </c>
+      <c r="F6" s="10">
+        <v>7914</v>
+      </c>
+      <c r="G6" s="10">
+        <v>2.55</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>SURFACE_WATER_RELEASE_IND</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <v>252913</v>
+      </c>
+      <c r="C7" s="10">
+        <v>81.62</v>
+      </c>
+      <c r="D7" s="10">
+        <v>38658</v>
+      </c>
+      <c r="E7" s="10">
+        <v>12.48</v>
+      </c>
+      <c r="F7" s="10">
+        <v>18301</v>
+      </c>
+      <c r="G7" s="10">
+        <v>5.91</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="14"/>
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Notes on missing values:
+All six indicators: Missing. Blank when the event has no linked area, and on area rows with incomplete reporting.</t>
+        </is>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
       <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:G9"/>
+    <mergeCell ref="A9:I10"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
